--- a/datasets/production-like-corpus/corpus/finance/FIN-002_2026差旅费用标准.xlsx
+++ b/datasets/production-like-corpus/corpus/finance/FIN-002_2026差旅费用标准.xlsx
@@ -540,7 +540,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -553,7 +553,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>文档ID：FIN-002    版本：V2.0    归口部门：FINANCE    生效日：2026-03-01</t>
+          <t>文档编号：NT-FINA-MAT-2026-002    版本：V2.0    归口部门：FINANCE    生效日：2026-03-01</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>核心商务城市；FIN-004：上海属于A类城市</t>
+          <t>核心商务城市；上海属于A类城市</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -731,7 +731,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>文档ID：FIN-002    版本：V2.0    归口部门：FINANCE    生效日：2026-03-01</t>
+          <t>文档编号：NT-FINA-MAT-2026-002    版本：V2.0    归口部门：FINANCE    生效日：2026-03-01</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>FIN-005：P6/P7上海住宿标准600元/晚</t>
+          <t>P6/P7上海住宿标准600元/晚；差旅费用标准以《2026差旅费用标准》为基准，而非员工手册</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -883,7 +883,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>文档ID：FIN-002    版本：V2.0    归口部门：FINANCE    生效日：2026-03-01</t>
+          <t>文档编号：NT-FINA-MAT-2026-002    版本：V2.0    归口部门：FINANCE    生效日：2026-03-01</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>FIN-011：国内差旅餐补按自然日计算</t>
+          <t>国内差旅餐补按自然日计算</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -987,7 +987,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>文档ID：FIN-002    版本：V2.0    归口部门：FINANCE    生效日：2026-03-01</t>
+          <t>文档编号：NT-FINA-MAT-2026-002    版本：V2.0    归口部门：FINANCE    生效日：2026-03-01</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>FIN-017：海外住宿按国家/地区标准表执行</t>
+          <t>海外住宿按国家/地区标准表执行</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>文档ID：FIN-002    版本：V2.0    归口部门：FINANCE    生效日：2026-03-01</t>
+          <t>文档编号：NT-FINA-MAT-2026-002    版本：V2.0    归口部门：FINANCE    生效日：2026-03-01</t>
         </is>
       </c>
     </row>
